--- a/data/trans_bre/P19C02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C02-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 12,64</t>
+          <t>-6,39; 12,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 8,88</t>
+          <t>-8,23; 8,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 10,91</t>
+          <t>-5,36; 9,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 6,23</t>
+          <t>-10,44; 6,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 46,42</t>
+          <t>-17,92; 48,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 42,58</t>
+          <t>-27,06; 40,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,71; 57,73</t>
+          <t>-20,15; 49,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,55; 14,0</t>
+          <t>-19,6; 15,12</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 6,84</t>
+          <t>-5,1; 7,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 12,04</t>
+          <t>-1,12; 11,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 11,49</t>
+          <t>-1,18; 12,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 5,01</t>
+          <t>-9,44; 4,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 31,24</t>
+          <t>-17,37; 31,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 57,06</t>
+          <t>-5,16; 53,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 46,7</t>
+          <t>-3,42; 50,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 15,86</t>
+          <t>-21,98; 15,21</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 3,68</t>
+          <t>-12,84; 3,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 12,8</t>
+          <t>-1,29; 13,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 8,86</t>
+          <t>-4,62; 8,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 9,33</t>
+          <t>-3,55; 9,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 14,54</t>
+          <t>-35,83; 12,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 61,78</t>
+          <t>-4,68; 65,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,54; 45,24</t>
+          <t>-17,52; 45,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,87; 46,64</t>
+          <t>-13,07; 47,63</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 6,49</t>
+          <t>-8,44; 6,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 9,0</t>
+          <t>-7,23; 8,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 6,29</t>
+          <t>-6,78; 6,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,13; -0,71</t>
+          <t>-29,39; -0,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,1; 25,91</t>
+          <t>-24,71; 25,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 35,84</t>
+          <t>-21,7; 31,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,89; 29,19</t>
+          <t>-24,19; 29,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-56,73; -2,15</t>
+          <t>-54,44; -1,86</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 12,1</t>
+          <t>-5,77; 12,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 14,63</t>
+          <t>-3,68; 13,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 12,22</t>
+          <t>-8,95; 13,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 6,35</t>
+          <t>-4,11; 6,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 73,68</t>
+          <t>-23,82; 75,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-14,78; 79,22</t>
+          <t>-13,87; 73,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-13,1; 19,68</t>
+          <t>-12,2; 20,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 7,61</t>
+          <t>-4,53; 7,77</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 6,53</t>
+          <t>-11,97; 7,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 4,71</t>
+          <t>-12,17; 4,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 16,8</t>
+          <t>-0,36; 16,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 8,22</t>
+          <t>-4,66; 8,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 21,77</t>
+          <t>-29,89; 24,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,97; 17,86</t>
+          <t>-35,87; 17,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 85,14</t>
+          <t>-1,65; 83,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-20,16; 56,65</t>
+          <t>-22,2; 54,28</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 4,56</t>
+          <t>-6,32; 4,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 9,94</t>
+          <t>-1,5; 9,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 8,55</t>
+          <t>-4,81; 8,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 36,0</t>
+          <t>-2,7; 34,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 19,2</t>
+          <t>-21,13; 20,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 38,93</t>
+          <t>-5,47; 39,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 29,22</t>
+          <t>-14,33; 27,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 84,63</t>
+          <t>-5,73; 71,39</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 9,53</t>
+          <t>-1,8; 9,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 1,23</t>
+          <t>-9,86; 1,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 4,36</t>
+          <t>-6,26; 4,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,84; 50,26</t>
+          <t>3,6; 47,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 35,43</t>
+          <t>-5,56; 35,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 3,22</t>
+          <t>-21,94; 3,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 8,71</t>
+          <t>-11,32; 9,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>6,05; 277,91</t>
+          <t>5,33; 215,74</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,19</t>
+          <t>-2,11; 2,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 4,1</t>
+          <t>-0,71; 4,14</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,01</t>
+          <t>-0,38; 5,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 18,45</t>
+          <t>-0,12; 19,1</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 11,65</t>
+          <t>-6,98; 10,64</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 14,36</t>
+          <t>-2,39; 14,47</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 14,8</t>
+          <t>-1,22; 15,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 48,32</t>
+          <t>-0,21; 50,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C02-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C02-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-5,47%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 12,82</t>
+          <t>-7,13; 12,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,23; 8,44</t>
+          <t>-6,86; 8,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 9,64</t>
+          <t>-5,36; 10,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 6,57</t>
+          <t>-6,22; 8,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 48,95</t>
+          <t>-19,15; 45,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 40,2</t>
+          <t>-24,2; 40,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 49,31</t>
+          <t>-20,04; 53,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,6; 15,12</t>
+          <t>-11,84; 19,39</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-1,46</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-5,71%</t>
+          <t>-3,96%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 7,32</t>
+          <t>-4,53; 7,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 11,11</t>
+          <t>-1,07; 11,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 12,23</t>
+          <t>-1,71; 12,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 4,88</t>
+          <t>-7,92; 4,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 31,28</t>
+          <t>-15,62; 35,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 53,23</t>
+          <t>-4,79; 53,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 50,03</t>
+          <t>-5,67; 50,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 15,21</t>
+          <t>-19,18; 14,5</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 3,49</t>
+          <t>-12,44; 2,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 13,35</t>
+          <t>-0,73; 13,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 8,54</t>
+          <t>-4,89; 8,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 9,48</t>
+          <t>-2,58; 9,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 12,72</t>
+          <t>-36,77; 10,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 65,66</t>
+          <t>-2,69; 64,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 45,12</t>
+          <t>-18,98; 46,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 47,63</t>
+          <t>-10,46; 49,26</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-13,07</t>
+          <t>-3,02</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-25,99%</t>
+          <t>-6,02%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 6,29</t>
+          <t>-8,8; 6,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 8,09</t>
+          <t>-6,58; 8,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 6,54</t>
+          <t>-7,7; 6,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,39; -0,77</t>
+          <t>-10,52; 5,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 25,18</t>
+          <t>-26,31; 24,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,7; 31,0</t>
+          <t>-19,64; 31,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 29,96</t>
+          <t>-26,94; 30,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,44; -1,86</t>
+          <t>-19,24; 12,39</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>2,36</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 12,42</t>
+          <t>-4,54; 14,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 13,97</t>
+          <t>-3,51; 14,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,95; 13,02</t>
+          <t>-10,4; 11,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 6,39</t>
+          <t>-3,19; 7,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,82; 75,4</t>
+          <t>-19,71; 81,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 73,33</t>
+          <t>-12,85; 84,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 20,97</t>
+          <t>-14,16; 18,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 7,77</t>
+          <t>-3,6; 8,56</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,13</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 7,4</t>
+          <t>-11,54; 7,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 4,3</t>
+          <t>-12,53; 3,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 16,6</t>
+          <t>-0,3; 15,74</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 8,01</t>
+          <t>-4,1; 7,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,89; 24,43</t>
+          <t>-29,11; 26,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,87; 17,03</t>
+          <t>-35,64; 14,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 83,45</t>
+          <t>-1,66; 81,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 54,28</t>
+          <t>-19,27; 55,39</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12,54</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>-1,42%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,69</t>
+          <t>-7,07; 4,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 9,86</t>
+          <t>-1,07; 10,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 8,13</t>
+          <t>-5,26; 7,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 34,58</t>
+          <t>-6,5; 4,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 20,09</t>
+          <t>-23,45; 20,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 39,81</t>
+          <t>-3,57; 40,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 27,94</t>
+          <t>-14,58; 25,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 71,39</t>
+          <t>-13,08; 11,4</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22,53</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 9,39</t>
+          <t>-1,5; 9,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 1,26</t>
+          <t>-10,14; 1,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 4,87</t>
+          <t>-6,34; 4,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,6; 47,34</t>
+          <t>1,02; 10,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 35,02</t>
+          <t>-4,72; 34,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 3,33</t>
+          <t>-22,28; 3,15</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 9,85</t>
+          <t>-11,24; 9,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,33; 215,74</t>
+          <t>1,52; 17,45</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6,25</t>
+          <t>1,49</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,9</t>
+          <t>-1,9; 3,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,14</t>
+          <t>-0,86; 4,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,15</t>
+          <t>-0,25; 5,2</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 19,1</t>
+          <t>-0,95; 3,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 10,64</t>
+          <t>-6,44; 11,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 14,47</t>
+          <t>-2,69; 14,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 15,31</t>
+          <t>-0,69; 15,56</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 50,78</t>
+          <t>-1,94; 8,52</t>
         </is>
       </c>
     </row>
